--- a/test_data/norfolk_coastal_flooding/benchmarking_frontier_minimal.xlsx
+++ b/test_data/norfolk_coastal_flooding/benchmarking_frontier_minimal.xlsx
@@ -989,7 +989,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sa_id</t>
+          <t>member_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
